--- a/data/transformed_data_2016.xlsx
+++ b/data/transformed_data_2016.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17541" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17538" uniqueCount="45">
   <si>
     <t>source</t>
   </si>
@@ -5109,7 +5109,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>16502.25097524893</v>
+        <v>16547.76217524893</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -5613,7 +5613,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>1438.6596</v>
+        <v>1484.1708</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -25111,7 +25111,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D194"/>
+  <dimension ref="A1:D193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25825,7 +25825,7 @@
         <v>5</v>
       </c>
       <c r="D51">
-        <v>1974.156716417911</v>
+        <v>2126.014925373135</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -25853,7 +25853,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>1063.007462686567</v>
+        <v>911.1492537313434</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -25993,7 +25993,7 @@
         <v>5</v>
       </c>
       <c r="D63">
-        <v>0.8932835820889977</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -26021,7 +26021,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>1879.54420858092</v>
+        <v>1880.437492163009</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -26992,16 +26992,16 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B135" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C135" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>150.964925373135</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -27029,7 +27029,7 @@
         <v>15</v>
       </c>
       <c r="D137">
-        <v>1734.98896719624</v>
+        <v>1885.953892569375</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -27524,10 +27524,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B173" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="C173" t="s">
         <v>15</v>
@@ -27538,10 +27538,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B174" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C174" t="s">
         <v>15</v>
@@ -27552,10 +27552,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B175" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C175" t="s">
         <v>15</v>
@@ -27566,10 +27566,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="C176" t="s">
         <v>15</v>
@@ -27580,10 +27580,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B177" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C177" t="s">
         <v>15</v>
@@ -27594,10 +27594,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B178" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C178" t="s">
         <v>15</v>
@@ -27608,10 +27608,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B179" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="C179" t="s">
         <v>15</v>
@@ -27622,10 +27622,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B180" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C180" t="s">
         <v>15</v>
@@ -27636,10 +27636,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B181" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="C181" t="s">
         <v>15</v>
@@ -27650,10 +27650,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B182" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="C182" t="s">
         <v>15</v>
@@ -27664,10 +27664,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B183" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="C183" t="s">
         <v>15</v>
@@ -27678,10 +27678,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C184" t="s">
         <v>15</v>
@@ -27692,10 +27692,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B185" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C185" t="s">
         <v>15</v>
@@ -27706,10 +27706,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B186" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C186" t="s">
         <v>15</v>
@@ -27720,10 +27720,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B187" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C187" t="s">
         <v>15</v>
@@ -27734,10 +27734,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C188" t="s">
         <v>15</v>
@@ -27748,7 +27748,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B189" t="s">
         <v>31</v>
@@ -27762,10 +27762,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C190" t="s">
         <v>15</v>
@@ -27776,7 +27776,7 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B191" t="s">
         <v>7</v>
@@ -27790,43 +27790,29 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B192" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C192" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B193" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="C193" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="D193">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4">
-      <c r="A194" t="s">
-        <v>30</v>
-      </c>
-      <c r="B194" t="s">
-        <v>42</v>
-      </c>
-      <c r="C194" t="s">
-        <v>44</v>
-      </c>
-      <c r="D194">
         <v>30000</v>
       </c>
     </row>
@@ -28509,7 +28495,7 @@
         <v>31</v>
       </c>
       <c r="D48">
-        <v>649.1297847646692</v>
+        <v>659.0575937534331</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -28719,7 +28705,7 @@
         <v>5</v>
       </c>
       <c r="D63">
-        <v>350.0052238805965</v>
+        <v>269.6802238805967</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -28747,7 +28733,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>3634.508882702476</v>
+        <v>3714.833882702475</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -29699,7 +29685,7 @@
         <v>43</v>
       </c>
       <c r="D133">
-        <v>4049.930531198275</v>
+        <v>4140.183340187039</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -29895,7 +29881,7 @@
         <v>5</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>80.325</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -43315,7 +43301,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>3058.087685917496</v>
+        <v>3057.712379913697</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -43651,7 +43637,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>6442.3632</v>
+        <v>6442.738506003799</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -73819,7 +73805,7 @@
         <v>4</v>
       </c>
       <c r="D158">
-        <v>44065.13032102244</v>
+        <v>43816.13032102244</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -74323,7 +74309,7 @@
         <v>4</v>
       </c>
       <c r="D194">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -79131,7 +79117,7 @@
         <v>4</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>237.8814627994956</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -79299,7 +79285,7 @@
         <v>4</v>
       </c>
       <c r="D158">
-        <v>5479.013786857198</v>
+        <v>5716.895249656694</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -79803,7 +79789,7 @@
         <v>4</v>
       </c>
       <c r="D194">
-        <v>4320</v>
+        <v>4320.000000000001</v>
       </c>
     </row>
     <row r="195" spans="1:4">

--- a/data/transformed_data_2016.xlsx
+++ b/data/transformed_data_2016.xlsx
@@ -5109,7 +5109,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>16547.76217524893</v>
+        <v>16502.25097524893</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -5613,7 +5613,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>1484.1708</v>
+        <v>1438.6596</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -28495,7 +28495,7 @@
         <v>31</v>
       </c>
       <c r="D48">
-        <v>659.0575937534331</v>
+        <v>649.1297847646692</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -28705,7 +28705,7 @@
         <v>5</v>
       </c>
       <c r="D63">
-        <v>269.6802238805967</v>
+        <v>350.0052238805965</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -28733,7 +28733,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>3714.833882702475</v>
+        <v>3634.508882702476</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -29685,7 +29685,7 @@
         <v>43</v>
       </c>
       <c r="D133">
-        <v>4140.183340187039</v>
+        <v>4049.930531198275</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -29881,7 +29881,7 @@
         <v>5</v>
       </c>
       <c r="D147">
-        <v>80.325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -43301,7 +43301,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>3057.712379913697</v>
+        <v>3058.087685917496</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -43637,7 +43637,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>6442.738506003799</v>
+        <v>6442.3632</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -73805,7 +73805,7 @@
         <v>4</v>
       </c>
       <c r="D158">
-        <v>43816.13032102244</v>
+        <v>44065.13032102244</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -74309,7 +74309,7 @@
         <v>4</v>
       </c>
       <c r="D194">
-        <v>249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -79117,7 +79117,7 @@
         <v>4</v>
       </c>
       <c r="D146">
-        <v>237.8814627994956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -79285,7 +79285,7 @@
         <v>4</v>
       </c>
       <c r="D158">
-        <v>5716.895249656694</v>
+        <v>5479.013786857198</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -79789,7 +79789,7 @@
         <v>4</v>
       </c>
       <c r="D194">
-        <v>4320.000000000001</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="195" spans="1:4">
